--- a/Data/hubs_data.xlsx
+++ b/Data/hubs_data.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497A95D8-CB24-4C55-A163-DCABA31A868C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -67,8 +73,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,13 +137,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,7 +189,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -209,6 +223,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -243,9 +258,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -418,11 +434,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,12 +465,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>51.5074</v>
+        <v>51.507399999999997</v>
       </c>
       <c r="C2">
         <v>-0.1278</v>
@@ -458,19 +481,16 @@
       <c r="E2">
         <v>0.05</v>
       </c>
-      <c r="F2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>53.4808</v>
+        <v>53.480800000000002</v>
       </c>
       <c r="C3">
-        <v>-2.2426</v>
+        <v>-2.2425999999999999</v>
       </c>
       <c r="D3">
         <v>750000</v>
@@ -478,19 +498,16 @@
       <c r="E3">
         <v>0.04</v>
       </c>
-      <c r="F3">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
-        <v>55.9533</v>
+        <v>55.953299999999999</v>
       </c>
       <c r="C4">
-        <v>-3.1883</v>
+        <v>-3.1882999999999999</v>
       </c>
       <c r="D4">
         <v>600000</v>
@@ -498,19 +515,16 @@
       <c r="E4">
         <v>0.06</v>
       </c>
-      <c r="F4">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>52.513</v>
+        <v>52.512999999999998</v>
       </c>
       <c r="C5">
-        <v>-1.8904</v>
+        <v>-1.8904000000000001</v>
       </c>
       <c r="D5">
         <v>450000</v>
@@ -518,11 +532,8 @@
       <c r="E5">
         <v>0.05</v>
       </c>
-      <c r="F5">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -538,19 +549,16 @@
       <c r="E6">
         <v>0.04</v>
       </c>
-      <c r="F6">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7">
-        <v>52.6309</v>
+        <v>52.630899999999997</v>
       </c>
       <c r="C7">
-        <v>1.2974</v>
+        <v>1.2974000000000001</v>
       </c>
       <c r="D7">
         <v>700000</v>
@@ -558,39 +566,33 @@
       <c r="E7">
         <v>0.06</v>
       </c>
-      <c r="F7">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
-        <v>54.9783</v>
+        <v>54.978299999999997</v>
       </c>
       <c r="C8">
-        <v>-1.6174</v>
+        <v>-1.6173999999999999</v>
       </c>
       <c r="D8">
         <v>650000</v>
       </c>
       <c r="E8">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F8">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9">
-        <v>53.8008</v>
+        <v>53.800800000000002</v>
       </c>
       <c r="C9">
-        <v>-1.5491</v>
+        <v>-1.5490999999999999</v>
       </c>
       <c r="D9">
         <v>550000</v>
@@ -598,19 +600,16 @@
       <c r="E9">
         <v>0.05</v>
       </c>
-      <c r="F9">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>50.3755</v>
+        <v>50.375500000000002</v>
       </c>
       <c r="C10">
-        <v>-4.1427</v>
+        <v>-4.1426999999999996</v>
       </c>
       <c r="D10">
         <v>720000</v>
@@ -618,28 +617,22 @@
       <c r="E10">
         <v>0.04</v>
       </c>
-      <c r="F10">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>55.8642</v>
+        <v>55.864199999999997</v>
       </c>
       <c r="C11">
-        <v>-4.2518</v>
+        <v>-4.2518000000000002</v>
       </c>
       <c r="D11">
         <v>600000</v>
       </c>
       <c r="E11">
         <v>0.06</v>
-      </c>
-      <c r="F11">
-        <v>12000</v>
       </c>
     </row>
   </sheetData>
